--- a/output/Tables/Description/Drivers/mean_km_short_drivers.xlsx
+++ b/output/Tables/Description/Drivers/mean_km_short_drivers.xlsx
@@ -373,13 +373,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1.408484734273868</v>
+        <v>1.130059326904374</v>
       </c>
       <c r="B2">
-        <v>1.380899315916587</v>
+        <v>1.107323305657111</v>
       </c>
       <c r="C2">
-        <v>1.436070152631148</v>
+        <v>1.152795348151638</v>
       </c>
     </row>
   </sheetData>
